--- a/inst/extdata/bsp_11.8_Tab_11.18_Trennung_Mortalitaet_Emigrationsrate_Skink-Population.xlsx
+++ b/inst/extdata/bsp_11.8_Tab_11.18_Trennung_Mortalitaet_Emigrationsrate_Skink-Population.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr date1904="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Henle/Documents/Dateien/Publikationen/Methodenbuch/Ulmer Texte/Daten/Online/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Gecko\Projects\Misc\Methodenbuch\Beispiele\final\Exceldateien\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B5DBF81-D11C-E545-81DA-4FDB9524F708}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{936441F5-CFDE-4097-8091-BE6C1AF1A241}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4700" yWindow="500" windowWidth="17620" windowHeight="14120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mb-ohneemig-Jolly-Seber" sheetId="1" r:id="rId1"/>
@@ -31,6 +31,9 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -512,10 +515,17 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="[$-407]mmmm\ yy;@"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13">
     <font>
       <sz val="10"/>
       <name val="Geneva"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -617,25 +627,25 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -719,9 +729,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022-Design">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 – 2022">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -759,7 +769,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 – 2022">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -865,7 +875,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 – 2022">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1016,20 +1026,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N140"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="10.81640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="11" width="10.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" ht="13">
       <c r="A1" s="6" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2">
       <c r="A2" s="10" t="s">
         <v>24</v>
       </c>
@@ -1037,12 +1047,12 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" ht="13">
       <c r="A4" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1050,7 +1060,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -1058,7 +1068,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -1066,7 +1076,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" ht="16.5">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -1074,7 +1084,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" ht="14.5">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -1082,7 +1092,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" ht="14.5">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -1090,7 +1100,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" ht="14.5">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -1098,7 +1108,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" ht="14.5">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -1106,7 +1116,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" ht="14.5">
       <c r="A13" s="10" t="s">
         <v>52</v>
       </c>
@@ -1114,7 +1124,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2" ht="14.5">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -1122,7 +1132,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2" ht="14.5">
       <c r="A15" s="11" t="s">
         <v>27</v>
       </c>
@@ -1130,7 +1140,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2" ht="14.5">
       <c r="A16" s="11" t="s">
         <v>28</v>
       </c>
@@ -1138,7 +1148,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" ht="15.5">
       <c r="A17" s="9" t="s">
         <v>25</v>
       </c>
@@ -1146,7 +1156,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" ht="15.5">
       <c r="A18" s="9" t="s">
         <v>7</v>
       </c>
@@ -1154,7 +1164,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" ht="14.5">
       <c r="A19" s="12" t="s">
         <v>33</v>
       </c>
@@ -1162,7 +1172,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="15" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" ht="14.5">
       <c r="A20" s="12" t="s">
         <v>31</v>
       </c>
@@ -1170,19 +1180,19 @@
         <v>32</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" ht="13">
       <c r="A22" s="6" t="s">
         <v>36</v>
       </c>
       <c r="C22" s="10"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" ht="13">
       <c r="A23" s="6" t="s">
         <v>37</v>
       </c>
       <c r="C23" s="10"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11">
       <c r="B24" s="10" t="s">
         <v>38</v>
       </c>
@@ -1211,7 +1221,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11">
       <c r="B25" s="10" t="s">
         <v>39</v>
       </c>
@@ -1243,7 +1253,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11">
       <c r="A26" s="13">
         <v>29951</v>
       </c>
@@ -1276,7 +1286,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11">
       <c r="A27" s="13">
         <v>30010</v>
       </c>
@@ -1306,7 +1316,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11">
       <c r="A28" s="13">
         <v>30071</v>
       </c>
@@ -1333,7 +1343,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11">
       <c r="A29" s="13">
         <v>30194</v>
       </c>
@@ -1357,7 +1367,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11">
       <c r="A30" s="13">
         <v>30255</v>
       </c>
@@ -1378,7 +1388,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:11">
       <c r="A31" s="13">
         <v>30316</v>
       </c>
@@ -1396,7 +1406,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11">
       <c r="A32" s="13">
         <v>30375</v>
       </c>
@@ -1411,7 +1421,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:11">
       <c r="A33" s="13"/>
       <c r="B33" s="10" t="s">
         <v>15</v>
@@ -1448,11 +1458,11 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:11">
       <c r="A34" s="13"/>
       <c r="B34" s="10"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:11">
       <c r="B35" s="10" t="s">
         <v>39</v>
       </c>
@@ -1460,7 +1470,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:11">
       <c r="B36">
         <v>1</v>
       </c>
@@ -1497,7 +1507,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:11">
       <c r="B37">
         <v>2</v>
       </c>
@@ -1530,7 +1540,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:11">
       <c r="B38">
         <v>3</v>
       </c>
@@ -1559,7 +1569,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:11">
       <c r="B39">
         <v>4</v>
       </c>
@@ -1584,7 +1594,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:11">
       <c r="B40">
         <v>5</v>
       </c>
@@ -1605,7 +1615,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:11">
       <c r="B41">
         <v>6</v>
       </c>
@@ -1622,7 +1632,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:11">
       <c r="B42">
         <v>7</v>
       </c>
@@ -1631,12 +1641,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:11" ht="13">
       <c r="A44" s="6" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:11">
       <c r="B46" s="4">
         <v>29951</v>
       </c>
@@ -1662,7 +1672,7 @@
         <v>30436</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:11">
       <c r="A47" t="s">
         <v>0</v>
       </c>
@@ -1691,7 +1701,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:11">
       <c r="A48" t="s">
         <v>1</v>
       </c>
@@ -1720,7 +1730,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:14">
       <c r="A49" t="s">
         <v>2</v>
       </c>
@@ -1757,7 +1767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:14">
       <c r="A50" t="s">
         <v>3</v>
       </c>
@@ -1796,7 +1806,7 @@
       <c r="L50" s="3"/>
       <c r="M50" s="3"/>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:14">
       <c r="A51" t="s">
         <v>4</v>
       </c>
@@ -1833,7 +1843,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:14">
       <c r="A52" t="s">
         <v>5</v>
       </c>
@@ -1868,7 +1878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:14" ht="15.5">
       <c r="A54" s="12" t="s">
         <v>43</v>
       </c>
@@ -1908,7 +1918,7 @@
       <c r="M54" s="2"/>
       <c r="N54" s="2"/>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:14">
       <c r="A55" t="s">
         <v>6</v>
       </c>
@@ -1948,7 +1958,7 @@
       <c r="M55" s="2"/>
       <c r="N55" s="2"/>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:14">
       <c r="A56" t="s">
         <v>7</v>
       </c>
@@ -1988,7 +1998,7 @@
       <c r="M56" s="1"/>
       <c r="N56" s="1"/>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:14">
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
@@ -2003,18 +2013,18 @@
       <c r="M57" s="1"/>
       <c r="N57" s="1"/>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:14" ht="13">
       <c r="A58" s="6" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:14" ht="13">
       <c r="A59" s="6" t="s">
         <v>36</v>
       </c>
       <c r="C59" s="10"/>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:14">
       <c r="B60" s="10" t="s">
         <v>38</v>
       </c>
@@ -2043,7 +2053,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:14">
       <c r="B61" s="10" t="s">
         <v>39</v>
       </c>
@@ -2075,7 +2085,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:14">
       <c r="A62" s="13">
         <v>29951</v>
       </c>
@@ -2108,7 +2118,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:14">
       <c r="A63" s="13">
         <v>30010</v>
       </c>
@@ -2138,7 +2148,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:14">
       <c r="A64" s="13">
         <v>30071</v>
       </c>
@@ -2165,7 +2175,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:11">
       <c r="A65" s="13">
         <v>30194</v>
       </c>
@@ -2189,7 +2199,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:11">
       <c r="A66" s="13">
         <v>30255</v>
       </c>
@@ -2210,7 +2220,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:11">
       <c r="A67" s="13">
         <v>30316</v>
       </c>
@@ -2228,7 +2238,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:11">
       <c r="A68" s="13">
         <v>30375</v>
       </c>
@@ -2243,7 +2253,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:11">
       <c r="A69" s="13"/>
       <c r="B69" s="10" t="s">
         <v>15</v>
@@ -2280,11 +2290,11 @@
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:11">
       <c r="A70" s="13"/>
       <c r="B70" s="10"/>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:11">
       <c r="B71" s="10" t="s">
         <v>39</v>
       </c>
@@ -2292,7 +2302,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:11">
       <c r="B72">
         <v>1</v>
       </c>
@@ -2329,7 +2339,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:11">
       <c r="B73">
         <v>2</v>
       </c>
@@ -2362,7 +2372,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:11">
       <c r="B74">
         <v>3</v>
       </c>
@@ -2391,7 +2401,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:11">
       <c r="B75">
         <v>4</v>
       </c>
@@ -2416,7 +2426,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:11">
       <c r="B76">
         <v>5</v>
       </c>
@@ -2437,7 +2447,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:11">
       <c r="B77">
         <v>6</v>
       </c>
@@ -2454,7 +2464,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:11">
       <c r="B78">
         <v>7</v>
       </c>
@@ -2463,12 +2473,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:11" ht="13">
       <c r="A80" s="6" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:14">
       <c r="B82" s="4">
         <v>29951</v>
       </c>
@@ -2494,7 +2504,7 @@
         <v>30436</v>
       </c>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:14">
       <c r="A83" t="s">
         <v>0</v>
       </c>
@@ -2523,7 +2533,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:14">
       <c r="A84" t="s">
         <v>1</v>
       </c>
@@ -2552,7 +2562,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:14">
       <c r="A85" t="s">
         <v>2</v>
       </c>
@@ -2589,7 +2599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:14">
       <c r="A86" t="s">
         <v>3</v>
       </c>
@@ -2628,7 +2638,7 @@
       <c r="L86" s="3"/>
       <c r="M86" s="3"/>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:14">
       <c r="A87" t="s">
         <v>4</v>
       </c>
@@ -2665,7 +2675,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:14">
       <c r="A88" t="s">
         <v>5</v>
       </c>
@@ -2700,7 +2710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:14" ht="15.5">
       <c r="A90" s="17" t="s">
         <v>33</v>
       </c>
@@ -2740,7 +2750,7 @@
       <c r="M90" s="2"/>
       <c r="N90" s="2"/>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:14">
       <c r="A91" s="10" t="s">
         <v>59</v>
       </c>
@@ -2780,7 +2790,7 @@
       <c r="M91" s="2"/>
       <c r="N91" s="2"/>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:14">
       <c r="A92" t="s">
         <v>7</v>
       </c>
@@ -2820,27 +2830,27 @@
       <c r="M92" s="1"/>
       <c r="N92" s="1"/>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:14" ht="13">
       <c r="A95" s="6" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:14">
       <c r="A96" s="10" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:7">
       <c r="A97" s="10" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:7">
       <c r="A98" s="10" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:7">
       <c r="A99" s="10" t="s">
         <v>52</v>
       </c>
@@ -2849,7 +2859,7 @@
         <v>1.3846153846153846</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:7">
       <c r="A100" s="12" t="s">
         <v>50</v>
       </c>
@@ -2878,7 +2888,7 @@
         <v>0.38502673796791453</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:7">
       <c r="A101" s="10" t="s">
         <v>7</v>
       </c>
@@ -2907,50 +2917,50 @@
         <v>0.61497326203208547</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:7">
       <c r="A102" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B102">
-        <f>B99*(B54-B90)/B100</f>
-        <v>6.9447228123622057E-2</v>
-      </c>
-      <c r="C102">
-        <f>B99*(C54-C90)/C100</f>
-        <v>0.14426754882477485</v>
-      </c>
-      <c r="D102">
-        <f>B99*(D54-D90)/D100</f>
-        <v>1.2222137346268411E-2</v>
-      </c>
-      <c r="E102">
-        <f>B99*(E54-E90)/E100</f>
-        <v>6.9662451381769519E-2</v>
-      </c>
-      <c r="F102">
-        <f>B99*(F54-F90)/F100</f>
-        <v>0</v>
-      </c>
-      <c r="G102">
-        <f>B99*(G54-G90)/G100</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B102" s="10">
+        <f>(B54-B90)/(B99*B54-B90)</f>
+        <v>0.13040646169880143</v>
+      </c>
+      <c r="C102" s="10">
+        <f>(C54-C90)/(B99*C54-C90)</f>
+        <v>0.27090239723763282</v>
+      </c>
+      <c r="D102" s="10">
+        <f>(D54-D90)/(B99*D54-D90)</f>
+        <v>2.2950457905770681E-2</v>
+      </c>
+      <c r="E102" s="10">
+        <f>(E54-E90)/(B99*E54-E90)</f>
+        <v>0.13081060315021167</v>
+      </c>
+      <c r="F102" s="10">
+        <f>(F54-F90)/(B99*F54-F90)</f>
+        <v>0</v>
+      </c>
+      <c r="G102" s="10">
+        <f>(G54-G90)/(B99*G54-G90)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7">
       <c r="A105" s="10" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:7">
       <c r="A106" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B106">
-        <f>1-F90*G90</f>
+      <c r="B106" s="10">
+        <f>1-F54*G54</f>
         <v>0.58072809543397774</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:7">
       <c r="A107" s="10" t="s">
         <v>54</v>
       </c>
@@ -2959,7 +2969,7 @@
         <v>0.58072809543397774</v>
       </c>
     </row>
-    <row r="140" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="140" spans="12:12">
       <c r="L140" s="1"/>
     </row>
   </sheetData>
